--- a/data/trans_camb/IP18A01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 7,17</t>
+          <t>-9,1; 7,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 2,04</t>
+          <t>-14,28; 1,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 47,89</t>
+          <t>-10,79; 46,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 11,71</t>
+          <t>-5,19; 11,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 7,79</t>
+          <t>-7,28; 7,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 29,55</t>
+          <t>-9,81; 21,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 7,01</t>
+          <t>-4,26; 7,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 2,44</t>
+          <t>-8,11; 3,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 21,56</t>
+          <t>-7,59; 21,13</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 106,75</t>
+          <t>-59,71; 105,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-88,6; 48,11</t>
+          <t>-89,4; 32,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 634,23</t>
+          <t>-100,0; 644,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 323,3</t>
+          <t>-50,64; 245,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 221,58</t>
+          <t>-72,67; 226,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 708,44</t>
+          <t>-100,0; 480,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 111,69</t>
+          <t>-36,0; 106,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,77; 49,96</t>
+          <t>-68,95; 51,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-73,02; 289,8</t>
+          <t>-75,29; 299,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,33</t>
+          <t>-1,4; 5,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,39</t>
+          <t>0,37; 6,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 6,19</t>
+          <t>-4,79; 6,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,42</t>
+          <t>-1,21; 5,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,84</t>
+          <t>-2,79; 3,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -0,32</t>
+          <t>-7,47; -0,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,28</t>
+          <t>-0,0; 4,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,07</t>
+          <t>-0,19; 4,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,9</t>
+          <t>-5,51; 0,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 97,3</t>
+          <t>-17,0; 91,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 124,97</t>
+          <t>2,29; 129,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,11; 107,15</t>
+          <t>-58,25; 97,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 82,33</t>
+          <t>-14,11; 75,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 43,26</t>
+          <t>-29,79; 49,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,88; -1,45</t>
+          <t>-82,15; -3,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 66,25</t>
+          <t>-0,64; 64,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 62,78</t>
+          <t>-3,26; 61,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,49; 13,36</t>
+          <t>-64,14; 9,86</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 6,16</t>
+          <t>-4,81; 6,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 0,26</t>
+          <t>-9,91; 0,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 7,07</t>
+          <t>-11,35; 6,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 5,53</t>
+          <t>-6,31; 4,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,92</t>
+          <t>-4,29; 6,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 4,5</t>
+          <t>-11,2; 3,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,04</t>
+          <t>-3,85; 3,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 2,34</t>
+          <t>-5,0; 2,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 1,22</t>
+          <t>-10,09; 1,95</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 75,4</t>
+          <t>-37,43; 88,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,65; 5,42</t>
+          <t>-73,43; 5,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,22</t>
+          <t>-100,0; 106,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,75; 88,47</t>
+          <t>-49,13; 69,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 97,05</t>
+          <t>-34,36; 95,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,24</t>
+          <t>-100,0; 79,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 48,38</t>
+          <t>-31,83; 49,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 28,37</t>
+          <t>-40,54; 35,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-87,62; 21,27</t>
+          <t>-90,83; 28,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 4,01</t>
+          <t>-1,38; 3,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,36</t>
+          <t>-1,61; 3,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 4,38</t>
+          <t>-5,31; 4,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,1</t>
+          <t>-1,1; 3,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,81</t>
+          <t>-2,05; 2,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -0,73</t>
+          <t>-6,94; -1,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,23</t>
+          <t>-0,55; 3,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,3</t>
+          <t>-1,25; 2,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,51; -0,4</t>
+          <t>-5,46; -0,43</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 56,93</t>
+          <t>-13,44; 54,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 47,06</t>
+          <t>-16,57; 49,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 57,88</t>
+          <t>-58,42; 55,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 58,24</t>
+          <t>-12,62; 55,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 39,57</t>
+          <t>-21,58; 39,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,7; -4,83</t>
+          <t>-77,02; -12,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 42,55</t>
+          <t>-5,92; 43,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 30,73</t>
+          <t>-13,3; 32,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,07; -1,72</t>
+          <t>-60,51; -4,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 7,0</t>
+          <t>-9,02; 7,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 1,57</t>
+          <t>-13,56; 1,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 46,11</t>
+          <t>-10,91; 42,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 11,52</t>
+          <t>-4,29; 11,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 7,78</t>
+          <t>-7,23; 7,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 21,93</t>
+          <t>-9,28; 24,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 7,29</t>
+          <t>-4,62; 6,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 3,1</t>
+          <t>-8,55; 2,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 21,13</t>
+          <t>-8,0; 21,29</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,71; 105,48</t>
+          <t>-59,45; 126,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-89,4; 32,92</t>
+          <t>-86,3; 61,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 644,37</t>
+          <t>-100,0; 635,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 245,91</t>
+          <t>-51,57; 290,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,67; 226,84</t>
+          <t>-72,22; 183,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 480,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 106,47</t>
+          <t>-37,93; 98,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,95; 51,26</t>
+          <t>-70,98; 36,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,29; 299,23</t>
+          <t>-77,95; 283,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,11</t>
+          <t>-1,12; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,9</t>
+          <t>0,86; 7,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 6,03</t>
+          <t>-4,64; 5,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 5,13</t>
+          <t>-1,03; 5,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,1</t>
+          <t>-3,23; 2,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -0,45</t>
+          <t>-7,5; -0,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,27</t>
+          <t>-0,16; 4,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,09</t>
+          <t>-0,27; 4,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,58</t>
+          <t>-5,29; 0,81</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 91,2</t>
+          <t>-13,37; 92,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 129,48</t>
+          <t>8,82; 133,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,25; 97,16</t>
+          <t>-57,83; 103,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 75,96</t>
+          <t>-11,77; 83,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,79; 49,55</t>
+          <t>-33,55; 39,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,15; -3,09</t>
+          <t>-81,57; 3,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 64,26</t>
+          <t>-2,08; 66,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 61,65</t>
+          <t>-3,73; 64,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,14; 9,86</t>
+          <t>-64,0; 12,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 6,52</t>
+          <t>-5,29; 6,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 0,22</t>
+          <t>-9,68; 0,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 6,66</t>
+          <t>-11,39; 6,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 4,76</t>
+          <t>-6,34; 5,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 6,9</t>
+          <t>-4,24; 6,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 3,55</t>
+          <t>-11,19; 3,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,95</t>
+          <t>-4,26; 3,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,86</t>
+          <t>-5,33; 2,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 1,95</t>
+          <t>-10,01; 1,1</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 88,17</t>
+          <t>-40,46; 85,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,43; 5,47</t>
+          <t>-71,3; 7,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 106,05</t>
+          <t>-100,0; 108,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 69,55</t>
+          <t>-49,11; 73,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 95,69</t>
+          <t>-34,21; 98,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,01</t>
+          <t>-100,0; 82,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 49,11</t>
+          <t>-34,83; 45,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 35,46</t>
+          <t>-44,15; 29,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,83; 28,06</t>
+          <t>-85,42; 20,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,93</t>
+          <t>-1,71; 3,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,65</t>
+          <t>-1,83; 3,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,05</t>
+          <t>-5,33; 4,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,97</t>
+          <t>-0,85; 4,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,69</t>
+          <t>-2,1; 2,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -1,04</t>
+          <t>-7,03; -0,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,19</t>
+          <t>-0,41; 3,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,44</t>
+          <t>-1,35; 2,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,46; -0,43</t>
+          <t>-5,44; 0,13</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 54,28</t>
+          <t>-16,84; 49,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 49,71</t>
+          <t>-19,13; 50,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 55,26</t>
+          <t>-58,45; 60,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 55,56</t>
+          <t>-9,26; 61,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 39,48</t>
+          <t>-21,95; 42,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,02; -12,91</t>
+          <t>-77,13; -3,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 43,4</t>
+          <t>-4,05; 42,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 32,1</t>
+          <t>-14,59; 29,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,51; -4,89</t>
+          <t>-59,58; 3,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,09</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,92</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,76</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-6,14</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>1,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 7,54</t>
+          <t>-4,8; 11,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 1,95</t>
+          <t>-7,8; 7,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 42,82</t>
+          <t>-9,3; 29,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 11,88</t>
+          <t>-9,53; 7,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 7,79</t>
+          <t>-14,55; 2,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 24,48</t>
+          <t>-10,76; 46,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 6,52</t>
+          <t>-4,68; 7,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 2,33</t>
+          <t>-8,42; 2,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 21,29</t>
+          <t>-7,6; 19,42</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41,87%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-2,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-12,52%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-6,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-53,61%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60,9%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>41,87%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-2,92%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,21%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,45; 126,1</t>
+          <t>-45,22; 323,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,3; 61,8</t>
+          <t>-72,63; 221,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 635,8</t>
+          <t>-100,0; 698,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 290,21</t>
+          <t>-59,22; 106,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,22; 183,06</t>
+          <t>-88,6; 48,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 614,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 98,53</t>
+          <t>-37,56; 111,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,98; 36,39</t>
+          <t>-70,77; 49,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-77,95; 283,32</t>
+          <t>-75,09; 253,76</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,02</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,97</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,99</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,94</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,41</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-2,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 5,37</t>
+          <t>-0,93; 5,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,33</t>
+          <t>-3,24; 2,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 5,75</t>
+          <t>-7,84; -1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 5,27</t>
+          <t>-1,11; 5,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,49</t>
+          <t>0,76; 7,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -0,16</t>
+          <t>-4,79; 6,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,37</t>
+          <t>-0,41; 4,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,22</t>
+          <t>-0,42; 4,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 0,81</t>
+          <t>-5,38; 0,68</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25,15%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-1,13%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-61,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>27,68%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>54,78%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,23%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-1,13%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-54,85%</t>
+          <t>-2,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-34,13%</t>
+          <t>-37,63%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 92,57</t>
+          <t>-11,47; 82,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 133,97</t>
+          <t>-34,14; 43,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,83; 103,49</t>
+          <t>-84,84; -15,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 83,18</t>
+          <t>-12,31; 97,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 39,35</t>
+          <t>5,84; 124,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,57; 3,46</t>
+          <t>-61,13; 106,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 66,66</t>
+          <t>-4,91; 66,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 64,08</t>
+          <t>-5,18; 62,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 12,67</t>
+          <t>-65,23; 10,57</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-5,05</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,48</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-5,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,32</t>
+          <t>-5,25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-5,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 6,68</t>
+          <t>-5,95; 5,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 0,45</t>
+          <t>-4,17; 6,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 6,88</t>
+          <t>-11,0; 5,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 5,1</t>
+          <t>-4,96; 6,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 6,79</t>
+          <t>-9,47; 0,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 3,91</t>
+          <t>-11,12; 9,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 3,76</t>
+          <t>-3,82; 4,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 2,23</t>
+          <t>-5,41; 2,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 1,1</t>
+          <t>-10,02; 2,28</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-5,98%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-51,21%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>5,06%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-42,64%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-53,35%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-5,98%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-53,92%</t>
+          <t>-49,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-53,8%</t>
+          <t>-50,74%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 85,96</t>
+          <t>-47,75; 88,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,3; 7,5</t>
+          <t>-33,58; 97,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 108,9</t>
+          <t>-100,0; 114,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 73,75</t>
+          <t>-38,23; 75,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 98,82</t>
+          <t>-70,65; 5,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,62</t>
+          <t>-100,0; 165,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 45,87</t>
+          <t>-32,1; 48,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 29,11</t>
+          <t>-43,87; 28,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-85,42; 20,66</t>
+          <t>-86,75; 40,56</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,55</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,64</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,86</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,31</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,07</t>
+          <t>-3,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,57</t>
+          <t>-1,03; 4,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,57</t>
+          <t>-2,43; 2,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,45</t>
+          <t>-7,44; -1,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 4,26</t>
+          <t>-1,29; 4,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,97</t>
+          <t>-1,65; 3,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,03; -0,53</t>
+          <t>-5,57; 4,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,17</t>
+          <t>-0,87; 3,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,25</t>
+          <t>-1,38; 2,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,13</t>
+          <t>-5,57; -0,44</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18,55%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-55,37%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>14,73%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>10,05%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-16,52%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-51,5%</t>
+          <t>-16,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-36,27%</t>
+          <t>-38,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 49,02</t>
+          <t>-10,87; 58,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 50,21</t>
+          <t>-24,46; 39,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 60,39</t>
+          <t>-79,29; -8,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 61,95</t>
+          <t>-13,43; 56,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 42,26</t>
+          <t>-16,95; 47,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,13; -3,61</t>
+          <t>-60,89; 60,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 42,69</t>
+          <t>-8,69; 42,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 29,35</t>
+          <t>-14,45; 30,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 3,98</t>
+          <t>-61,71; -3,94</t>
         </is>
       </c>
     </row>
